--- a/GameConfig/Datas/剧情节点配置表.xlsx
+++ b/GameConfig/Datas/剧情节点配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="剧情节点配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剧情节点配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,46 @@
           <t>isSessionEnd</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>defaultNextNodeId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>minAffection</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>turnType</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>animationAsset</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>onEnterActionIds</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onExitActionIds</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>extraNextNodeIds</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,6 +532,46 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,6 +609,46 @@
           <t>c</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,30 +686,4162 @@
           <t>是否会话结束</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>默认后继节点</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>最低说话人好感</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Turn类型</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>演出资源</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>进入动作</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>离开动作</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>额外后继候选</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>节点优先级</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>N01</t>
+          <t>T0101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NPC_001</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>今天路过这里的时候，我突然想起了一件以前的事。</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>R01</t>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>周老，我就直说了。三十天，整条街都得搬完。您这儿是最后一户。</t>
         </is>
       </c>
       <c r="G5" t="b">
         <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>T0102</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T0102</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>他们的东西还在里头，有几件都是上代人留下来的了，搬一下就得散。</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>T0103</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T0103</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>编号登记，集中转运，有损坏走保险赔付。流程都给您交待过了，还有什么担心的呢？</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>T0104</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T0104</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>赔付？街坊邻里把东西交给我，他们是想修好了，不是要你们赔的钱！</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>T0105</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T0105</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>周老，您知道我不是来和您讨价还价的。</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>T0106</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T0106</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>我也没和你讨价还价，我就一句话，这些东西修不完，我就不走。</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>T0107</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T0107</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>您说的修完，大概要多久？</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>T0108</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T0108</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>一件要两周。</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>T0109</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T0109</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>一件能用得了两周？</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>T0110</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>T0110</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>那你问问他呗</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>T0111</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>T0111</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>你来看看，这件修复好需要多久？</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>O011101,O011102</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>T0111</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ADD_CAMERA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>REMOVE_CAMERA</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>T0112</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>……有几件？</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>T0114</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T0113</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>……有几件？（跳转测试）</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>T0114</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>T0114</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>还有三件。</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>T0115</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T0115</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>那就是120天！周老，您这是在要求我私自给您四个月的延期，而理由仅仅是“人情”。</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>T0116</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>T0116</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>T0117</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T0117</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>您知道我做不到。周老，搬迁的文件说得很清楚，无效低效的东西，一律需要丢弃，不能影响搬迁效率，所以按照条例，这些东西您本应全部扔掉。</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>T0118</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>T0118</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>可那些是街坊邻里给我的信任！那些东西，是街坊的记忆！</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>T0119</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>T0119</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>……您说信任，说记忆，可它们现在能值多少？不能量化的东西，就算我认，上头也不会认。</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>T0120</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>T0120</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>我说过了，东西没修完，我就不走。</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>T0121</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>T0121</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>周老，街区清退率已经落到全市倒数第三。每个小时我都在向总调度解释"为什么这一户还没完成"。您跟我说人情，我肩上压的是整条街的时效。</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>T0122</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>T0122</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>我不是拦你。我是想让你知道，有些东西你一转身，就再也找不回来了。你把它登记成“可赔付”，赔的是钱，赔不回你爸坐在那儿看字、说看不清的样子。</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>T0123</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>T0123</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>那您告诉我怎么办？！让我跟总调度说“这一户要等，因为一副旧眼镜有感情”？您觉得他们会认？！——在他们那儿感情是干扰项，是无效值！</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>T0124</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>T0124</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>那你呢，你认吗？</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>T0125</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>T0125</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>……我认不认，有区别吗？周老，您也不用拿什么旧物有情来塞我，就算真的过了我这关，上头也不会让您过这一关的。</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>T0126</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>T0126</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>所以你还是——</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>T0127</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>T0127</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>今天下班前，我要这个柜子里所有物件的清单和处置意见。能转运的转运，不能转运的……走评估程序。</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>T0128</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>T0128</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>评估？评估什么？</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>T0129</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>T0129</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>估值。系统要一个可量化的结果，来决定丢还是留，有没有价值留。具体怎么评——交给它吧。</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>T0130</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>T0130</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>——一个机器？</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>T0131</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>T0131</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>它没有立场，不认人情，只认它算出来的数。您说这副眼镜值我爸在这儿坐的半下午——它算不算得出来，是它的事。您只要把东西交给它，等一个结果。</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>T0132</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>T0132</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>我修了四十七年东西，从来没让人用秤这样称过人心。</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>T0133</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>T0133</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>那就从今天开始。周师傅，您的老规矩，现在要过一道机器的手了。</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>T0134</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>T0134</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>……好。那就现在，你在这看着，它在你们这可笑的量化标准下，到底值多少。</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>T0135</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>T0135</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>你，——说说看？</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>O013301,O013302</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ADD_GLASS</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>REMOVE_GLASS</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>T0201</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>……喂，你除了评估物品之外，还能做什么？</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>O020101</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ANY,5,101,T0203</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>T0202</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>T0203</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>T0202</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>你上次说那眼镜该丢，哼……果然跟那些冷血的所谓“上头”一样，也对你毕竟是他们“耗尽心血”搞出来的玩意儿。</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>T0203</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>T0203</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>虽然你上次说那眼镜不该丢，我还挺高兴的，但这不代表我认可你，和创造你的那些人的观念。</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>T0204</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>T0204</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>罢了，该不该的，现在再说也没什么意义了。我这有个老座钟你来看看</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>O020601,O020602</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>T0205</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ADD_CLOCK</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>REMOVE_CLOCK</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>T0205</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>这钟，是我的一个老朋友留给我的。</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>T0206</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>T0206</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>十几年前吧，他把这钟拿了过来，然后说，“老周啊，我得出趟远门，这钟你修好了就先替我保管着吧，等我回来再找你拿。”后来我才知道，他是出国了，漂洋过海，去赚外国人的钱，这一去啊，就是十年。</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>T0207</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>T0207</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>几年前他回来了，落地头一件事，就是来我这里拿那钟表，但我没能拿得出来。——因为东西太多了。他走的十年里，修理铺人来人往，每天都有数不清的旧物件等着我修，我便总觉得，拖一拖，再拖一拖，问题不大。直到那天，他真的出现在我面前，问我，“老周，还记得我吗？我来拿十几年前那座钟来了。”</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>T0208</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>T0208</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>可我拿不出来。……我拿不出来啊。它被我忘在仓库不知道哪个角落里了，被埋了十几年，没被我拿出来看过，更别提修。</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>T0209</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>T0209</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>不说这个了。搬迁令果然不给延期。</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>T0210</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>T0210</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>四十天后，你也会被封存吧？毕竟，博物馆也拆了，老街也拆了——没什么可以给你评估的了。</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>T0211</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>T0211</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>都一样啊，老物件，丢掉了；老院落，搬走了；接着……又会是什么？</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>T0301</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>你能看看它吗？它叫小白。这里开线了，可要是把这一块换掉，摸起来就不一样了。</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>T0302</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>ADD_DOLL</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>T0302</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>填充棉已经结块，缝线也老化了。按维修成本算，买一个新的更划算。你觉得还值得修吗？</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>O030201,O030202</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>T0303</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>T0303</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>你没有马上说它没用了。小满以前也会把它抱在怀里，哪怕我们只是坐在门口等大人下班。</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>T0305</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>joyful</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>T0304</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>我知道新的一定更干净，也更结实。可是它不是小满送我的那一个。</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>T0305</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>T0305</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>你检查的时候发现它里面像是还有一层夹布。你想怎么告诉我？</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>O030501,O030502</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>T0307</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>T0306</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>这是小满写的。她搬走那天塞进去的……我一直以为她什么都没留下。谢谢你让我知道。</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>T0307</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>好，那就先把它补好。以后我会自己告诉小白，小满以前怎么陪我等过人。</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>T0401</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>这台收音机是我父亲留下来的。妻子想让我修好它，我本来觉得没必要。你先帮我看看，里面还有没有能用的部分。</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>T0402</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>ADD_RADIO_DAD</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>T0402</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>读取模块坏了，存储部分看起来还在。先记录故障，还是现在就试着接通？</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>O040201,O040202</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>T0403</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>T0403</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>先记下来吧。至少别让里面可能还在的东西，因为我想快点修好而一起坏掉。</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>T0405</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>T0404</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>如果只是接触不良，或许还能读出来。你把步骤告诉我，我自己来。</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>T0405</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>T0405</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>我按你给的办法试过了。旧接口断裂，替代零件也停产，焊接点太细，我没能接稳。现在要不要继续？</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>O040501,O040502</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>T0406</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>T0406</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>先停在这里吧。至少存储部分还在。知道该怎么修，和真的修得好，中间隔着很多东西。</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>T0407</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>我不想把失败写成什么都没做成。你把我试过的步骤也留在记录里吧。</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>T0501</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>昨天我妻子打来电话，问收音机修得怎么样。她说里面有重要的东西，还准备给陈果一份礼物。问到是什么，她又没说完。</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>T0502</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>T0502</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>她希望我在一个重要日子之前修好，但没有说那天是什么。我要不要再问清楚？</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>O050201,O050202</t>
+        </is>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>T0503</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>T0503</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>她说礼物已经准备好了。她不想催我，只是希望这次我们一家能一起听完那段录音。</t>
+        </is>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>T0505</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>T0504</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>你说得对。我不想把她的期待拆成一条条待办，但我也确实想知道收音机里留下了什么。</t>
+        </is>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>T0505</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>T0505</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>这次维修不只是我一个人的事。你觉得我该把它当成什么？</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>O050501,O050502</t>
+        </is>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>T0506</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>T0506</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>是啊，家里每个人都记得一点，但谁也没有把它们放在一起。等修好之后，我们一起听。</t>
+        </is>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>joyful</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>T0507</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>先把能做的做好。等我准备好了，再问她录音里是什么。</t>
+        </is>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>T0601</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>陈先生那台收音机缺个同型号的零件。我自己的机器里有一件能用的。拆下来，或许就能让他的收音机响起来。</t>
+        </is>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>T0602</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>ADD_RADIO_ZHOU</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>T0602</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>这台里头也留着我老朋友的声音。拆了零件，机器就未必还能响。你觉得我该先做什么？</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>O060201,O060202</t>
+        </is>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>T0603</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>T0603</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>我不是没想过把它留着。只是看着它在架子上，我就觉得那个人还没有走远。</t>
+        </is>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>T0605</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>T0604</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>你想先确认损坏程度。好，我把外壳打开给你看。只要还能留住声音，我也想知道有没有别的办法。</t>
+        </is>
+      </c>
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>T0605</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>T0605</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>零件就在这里。要是拆下来，收音机可能就再也不能播放那段声音。你还想劝我吗？</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>O060501,O060502</t>
+        </is>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>T0606</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>T0606</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>我还是决定拆。那边的收音机修好，至少还有一家人能坐在一起听。至于我的这台……我会记得它为什么在这里。</t>
+        </is>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>T0607</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>我知道你担心这段声音会消失。我也担心。但有些东西留在原处，有些东西得交给别人继续用。</t>
+        </is>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>T0701</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>老周的零件装好了。收音机能通电了。陈果和她妈妈也来了。你觉得现在就播放吗？</t>
+        </is>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>T0702</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>joyful</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>ADD_RADIO_REPAIRED</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>T0702</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>录音里可能有我父亲留下的话。要不要现在听完？</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>O070201,O070202</t>
+        </is>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>T0703</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>T0703</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>爸爸刚才叫我小时候的小名。我都快忘了他以前这么叫我。</t>
+        </is>
+      </c>
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>T0705</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>T0704</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>我本来以为只是些旧录音。听见他的声音之后，才发现有些话我一直没敢再想。</t>
+        </is>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>T0705</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>T0705</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>录音中间停了一会儿。你觉得我们还要继续听吗？</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>O070501,O070502</t>
+        </is>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>T0706</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>T0706</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>陈果</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>再放一遍吧。我想记住他叫我的声音。妈妈，你也坐近一点。</t>
+        </is>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>joyful</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>T0707</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>先停一会儿吧。我们不用把每一段声音都解释清楚。今天能一起听见它，已经够了。</t>
+        </is>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>T0801</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>更新通知已经发到你的终端了。系统要求清理超限记忆，把工作状态恢复到稳定版本。它让我确认哪些记录可以删。</t>
+        </is>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>T0802</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>T0802</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>如果必须整理，你希望系统先按什么标准排列？</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>O080201,O080202</t>
+        </is>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>T0803</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>T0803</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>使用频率确实能说明哪些资料常被调用，却没法说明一段很少提起的经历是否已经改变了你。</t>
+        </is>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>T0805</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>T0804</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>关联也许不能当作系统指标。但你保留下来的记录，已经不只是彼此独立的信息了。</t>
+        </is>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>T0805</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>T0805</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>通知要求今晚完成清理。你要我替系统选一个排序规则，还是把选择留给你？</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>O080501,O080502</t>
+        </is>
+      </c>
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>T0806</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>T0806</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>我会把列表交给你。删掉哪一段，应该由真正经历过它的你决定。</t>
+        </is>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>T0807</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>好，我不替你挑。更新时会要求至少腾出空间。你可以慢慢看完每一段再决定。</t>
+        </is>
+      </c>
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T0901</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>更新完以后，你把我叫错了一次。我问你还记不记得那座钟，你说找不到那条记录。你现在还好吗？</t>
+        </is>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>T0902</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>T0902</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>如果记录不在了，你还愿意听我重新讲一遍吗？</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>O090201,O090202</t>
+        </is>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>T0904</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>T0903</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>你还记得布偶里的纸条。那就先从小满那天搬走的事讲起吧。</t>
+        </is>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>T0905</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>joyful</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>T0904</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>你不记得纸条也没关系。我可以再讲一次。你没有把我打断，也没有催我快点说完。</t>
+        </is>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>T0905</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>T0905</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>这次你没有查出维修成本，也没有恢复旧记录。可你还是问我想不想继续说。你为什么这么做？</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>O090501,O090502</t>
+        </is>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>T0906</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>T0906</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>你还记得我朋友的收音机。就算叫不出那段记忆的名字，你也知道我不想把它扔掉。</t>
+        </is>
+      </c>
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>T0907</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>说不清也没关系。你停下来听我说，这已经是新的回应了。</t>
+        </is>
+      </c>
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>T1001</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>老街清退的日子快到了。有人想把旧物集中转运，有人只想带走陪了自己很多年的那几件。系统问你，怎样安排最有效率。</t>
+        </is>
+      </c>
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>T1002</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>T1002</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>你准备怎么给出最后一份评估？</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>O100201,O100202</t>
+        </is>
+      </c>
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>T1003</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>T1003</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>你给出的方案很清楚，时间和运输成本都最低。但这次，你没有把“谁来决定”也交给系统。</t>
+        </is>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>T1005</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>T1004</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>你把清单交还给了每个物主。事情会慢一些，但他们可以自己决定要带走什么。</t>
+        </is>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>T1005</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>T1005</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>系统要求你给出最优方案。你刚才作出的选择，还是它算出来的吗？</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>O100501,O100502</t>
+        </is>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>T1006</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>thoughtful</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>T1006</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>你没有替所有人保留所有东西，也没有把他们的选择压成一个数字。你给出了评估，也把决定权留给了他们。</t>
+        </is>
+      </c>
+      <c r="G105" t="b">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>T1007</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>你说这是你的选择。也许你已经不记得每一段经历，可它们没有白白经过你。</t>
+        </is>
+      </c>
+      <c r="G106" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>joyful</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/剧情节点配置表.xlsx
+++ b/GameConfig/Datas/剧情节点配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="剧情节点配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剧情节点配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2286,11 +2286,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>T0203</t>
@@ -2336,7 +2331,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -2379,7 +2374,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -2422,7 +2417,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -2468,11 +2463,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>ADD_CLOCK</t>
@@ -2523,7 +2513,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -2566,7 +2556,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -2609,7 +2599,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -2652,7 +2642,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -2695,7 +2685,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -2738,7 +2728,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -2781,7 +2771,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -2824,7 +2814,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -2862,7 +2852,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -2905,7 +2895,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -2948,7 +2938,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -2991,7 +2981,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -3034,7 +3024,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -3077,7 +3067,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O57" t="n">
@@ -3120,7 +3110,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -3163,7 +3153,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -3206,7 +3196,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -3249,7 +3239,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -3335,7 +3325,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -3378,7 +3368,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -3421,7 +3411,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3474,7 +3464,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -3522,7 +3512,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -3565,7 +3555,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -3608,7 +3598,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -3651,7 +3641,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -3694,7 +3684,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -3735,11 +3725,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
@@ -3780,7 +3765,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -3823,7 +3808,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -3866,7 +3851,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -3909,7 +3894,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -3947,7 +3932,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -3990,7 +3975,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4043,7 +4028,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -4086,7 +4071,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -4134,7 +4119,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -4177,7 +4162,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -4220,7 +4205,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -4263,7 +4248,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -4306,7 +4291,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -4349,7 +4334,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -4387,7 +4372,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -4428,11 +4413,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
@@ -4473,7 +4453,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -4514,11 +4494,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
@@ -4559,7 +4534,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -4600,11 +4575,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O92" t="n">
         <v>1</v>
       </c>
@@ -4645,7 +4615,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -4686,11 +4656,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
@@ -4731,7 +4696,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -4777,11 +4742,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>ADD_RADIO</t>
@@ -4832,7 +4792,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -4873,11 +4833,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O98" t="n">
         <v>1</v>
       </c>
@@ -4918,7 +4873,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -4959,11 +4914,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O100" t="n">
         <v>1</v>
       </c>
@@ -5004,7 +4954,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -5045,11 +4995,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
@@ -5090,7 +5035,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -5133,7 +5078,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -5174,11 +5119,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
@@ -5219,7 +5159,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -5260,11 +5200,6 @@
           <t>NpcDialogue</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O107" t="n">
         <v>1</v>
       </c>
@@ -5305,7 +5240,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -5348,7 +5283,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -5391,7 +5326,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -5434,7 +5369,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -5475,11 +5410,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
@@ -5518,11 +5448,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
@@ -5561,11 +5486,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O114" t="n">
         <v>1</v>
       </c>
@@ -5606,7 +5526,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -5647,11 +5567,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
@@ -5697,7 +5612,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -5745,7 +5660,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -5788,7 +5703,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -5831,7 +5746,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -5874,7 +5789,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -5917,7 +5832,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -5960,7 +5875,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -6003,7 +5918,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -6046,7 +5961,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -6089,7 +6004,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -6132,7 +6047,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -6175,7 +6090,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -6218,7 +6133,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -6261,7 +6176,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -6304,7 +6219,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -6347,7 +6262,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -6395,7 +6310,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O133" t="n">
@@ -6438,7 +6353,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O134" t="n">
@@ -6481,7 +6396,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -6524,7 +6439,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -6567,7 +6482,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -6610,7 +6525,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O138" t="n">
@@ -6653,7 +6568,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O139" t="n">
@@ -6696,7 +6611,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -6739,7 +6654,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -6782,7 +6697,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -6820,7 +6735,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -6863,7 +6778,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -6906,7 +6821,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -6949,7 +6864,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -6992,7 +6907,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -7035,7 +6950,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O148" t="n">
@@ -7078,7 +6993,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O149" t="n">
@@ -7126,7 +7041,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -7179,7 +7094,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -7222,7 +7137,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -7265,7 +7180,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O153" t="n">
@@ -7308,7 +7223,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -7351,7 +7266,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O155" t="n">
@@ -7394,7 +7309,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O156" t="n">
@@ -7437,7 +7352,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -7480,7 +7395,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O158" t="n">
@@ -7521,11 +7436,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O159" t="n">
         <v>1</v>
       </c>
@@ -7564,11 +7474,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O160" t="n">
         <v>1</v>
       </c>
@@ -7607,11 +7512,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O161" t="n">
         <v>1</v>
       </c>
@@ -7650,11 +7550,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O162" t="n">
         <v>1</v>
       </c>
@@ -7693,11 +7588,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O163" t="n">
         <v>1</v>
       </c>
@@ -7736,11 +7626,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O164" t="n">
         <v>1</v>
       </c>
@@ -7779,11 +7664,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O165" t="n">
         <v>1</v>
       </c>
@@ -7822,11 +7702,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O166" t="n">
         <v>1</v>
       </c>
@@ -7865,11 +7740,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O167" t="n">
         <v>1</v>
       </c>
@@ -7908,11 +7778,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O168" t="n">
         <v>1</v>
       </c>
@@ -7951,11 +7816,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O169" t="n">
         <v>1</v>
       </c>
@@ -7994,11 +7854,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O170" t="n">
         <v>1</v>
       </c>
@@ -8037,11 +7892,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O171" t="n">
         <v>1</v>
       </c>
@@ -8080,11 +7930,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O172" t="n">
         <v>1</v>
       </c>
@@ -8123,11 +7968,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O173" t="n">
         <v>1</v>
       </c>
@@ -8166,11 +8006,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O174" t="n">
         <v>1</v>
       </c>
@@ -8209,11 +8044,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O175" t="n">
         <v>1</v>
       </c>
@@ -8252,11 +8082,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O176" t="n">
         <v>1</v>
       </c>
@@ -8295,11 +8120,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O177" t="n">
         <v>1</v>
       </c>
@@ -8338,11 +8158,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O178" t="n">
         <v>1</v>
       </c>
@@ -8381,11 +8196,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O179" t="n">
         <v>1</v>
       </c>
@@ -8424,11 +8234,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O180" t="n">
         <v>1</v>
       </c>
@@ -8467,11 +8272,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O181" t="n">
         <v>1</v>
       </c>
@@ -8512,7 +8312,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O182" t="n">
@@ -8560,7 +8360,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O183" t="n">
@@ -8603,7 +8403,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O184" t="n">
@@ -8646,7 +8446,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O185" t="n">
@@ -8689,7 +8489,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O186" t="n">
@@ -8732,7 +8532,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O187" t="n">
@@ -8775,7 +8575,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O188" t="n">
@@ -8823,7 +8623,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O189" t="n">
@@ -8866,7 +8666,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O190" t="n">
@@ -8909,7 +8709,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O191" t="n">
@@ -8952,7 +8752,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O192" t="n">
@@ -8995,7 +8795,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -9038,7 +8838,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O194" t="n">
@@ -9081,7 +8881,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O195" t="n">
@@ -9124,7 +8924,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O196" t="n">
@@ -9167,7 +8967,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O197" t="n">
@@ -9210,7 +9010,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O198" t="n">
@@ -9253,7 +9053,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O199" t="n">
@@ -9296,7 +9096,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O200" t="n">
@@ -9339,7 +9139,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O201" t="n">
@@ -9382,7 +9182,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="O202" t="n">
@@ -9420,7 +9220,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O203" t="n">
@@ -9463,7 +9263,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O204" t="n">
@@ -9504,11 +9304,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O205" t="n">
         <v>1</v>
       </c>
@@ -9549,7 +9344,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O206" t="n">
@@ -9592,7 +9387,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O207" t="n">
@@ -9635,7 +9430,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O208" t="n">
@@ -9678,7 +9473,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O209" t="n">
@@ -9726,7 +9521,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O210" t="n">
@@ -9769,7 +9564,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O211" t="n">
@@ -9812,7 +9607,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O212" t="n">
@@ -9855,7 +9650,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O213" t="n">
@@ -9898,7 +9693,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O214" t="n">
@@ -9941,7 +9736,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O215" t="n">
@@ -9982,11 +9777,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O216" t="n">
         <v>1</v>
       </c>
@@ -10027,7 +9817,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O217" t="n">
@@ -10070,7 +9860,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O218" t="n">
@@ -10118,7 +9908,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O219" t="n">
@@ -10159,11 +9949,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O220" t="n">
         <v>1</v>
       </c>
@@ -10204,7 +9989,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O221" t="n">
@@ -10247,7 +10032,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O222" t="n">
@@ -10290,7 +10075,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>moved</t>
         </is>
       </c>
       <c r="O223" t="n">
@@ -10333,7 +10118,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O224" t="n">
@@ -10376,7 +10161,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O225" t="n">
@@ -10414,7 +10199,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O226" t="n">
@@ -10455,11 +10240,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O227" t="n">
         <v>1</v>
       </c>
@@ -10498,11 +10278,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O228" t="n">
         <v>1</v>
       </c>
@@ -10541,11 +10316,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O229" t="n">
         <v>1</v>
       </c>
@@ -10584,11 +10354,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O230" t="n">
         <v>1</v>
       </c>
@@ -10627,11 +10392,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O231" t="n">
         <v>1</v>
       </c>
@@ -10670,11 +10430,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>GRANT_EMOTION_SELF</t>
@@ -10718,11 +10473,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O233" t="n">
         <v>1</v>
       </c>
@@ -10761,11 +10511,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O234" t="n">
         <v>1</v>
       </c>
@@ -10804,11 +10549,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O235" t="n">
         <v>1</v>
       </c>
@@ -10847,11 +10587,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O236" t="n">
         <v>1</v>
       </c>
@@ -10890,11 +10625,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O237" t="n">
         <v>1</v>
       </c>
@@ -10933,11 +10663,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O238" t="n">
         <v>1</v>
       </c>
@@ -10976,11 +10701,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O239" t="n">
         <v>1</v>
       </c>
@@ -11019,11 +10739,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O240" t="n">
         <v>1</v>
       </c>
@@ -11062,11 +10777,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O241" t="n">
         <v>1</v>
       </c>
@@ -11105,11 +10815,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O242" t="n">
         <v>1</v>
       </c>
@@ -11148,11 +10853,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O243" t="n">
         <v>1</v>
       </c>
@@ -11191,11 +10891,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O244" t="n">
         <v>1</v>
       </c>
@@ -11234,11 +10929,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O245" t="n">
         <v>1</v>
       </c>
@@ -11277,11 +10967,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O246" t="n">
         <v>1</v>
       </c>
@@ -11320,11 +11005,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O247" t="n">
         <v>1</v>
       </c>
@@ -11363,11 +11043,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O248" t="n">
         <v>1</v>
       </c>
@@ -11406,11 +11081,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O249" t="n">
         <v>1</v>
       </c>
@@ -11449,11 +11119,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O250" t="n">
         <v>1</v>
       </c>
@@ -11492,11 +11157,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O251" t="n">
         <v>1</v>
       </c>
@@ -11537,7 +11197,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O252" t="n">
@@ -11580,7 +11240,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O253" t="n">
@@ -11623,7 +11283,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O254" t="n">
@@ -11666,7 +11326,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O255" t="n">
@@ -11709,7 +11369,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O256" t="n">
@@ -11752,7 +11412,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O257" t="n">
@@ -11795,7 +11455,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O258" t="n">
@@ -11838,7 +11498,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O259" t="n">
@@ -11881,7 +11541,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O260" t="n">
@@ -11924,7 +11584,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O261" t="n">
@@ -11967,7 +11627,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>thoughtful</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O262" t="n">
@@ -12008,11 +11668,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O263" t="n">
         <v>1</v>
       </c>
@@ -12051,11 +11706,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O264" t="n">
         <v>1</v>
       </c>
@@ -12094,11 +11744,6 @@
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
-        </is>
-      </c>
       <c r="O265" t="n">
         <v>1</v>
       </c>
@@ -12130,11 +11775,6 @@
       <c r="J266" t="inlineStr">
         <is>
           <t>PlayerDialogue</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>thoughtful</t>
         </is>
       </c>
       <c r="O266" t="n">

--- a/GameConfig/Datas/剧情节点配置表.xlsx
+++ b/GameConfig/Datas/剧情节点配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P267"/>
+  <dimension ref="A1:R267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,16 @@
           <t>backgroundId</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inspectGate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>hideOtherNpc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -595,6 +605,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,6 +697,16 @@
           <t>c</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -759,6 +789,16 @@
           <t>本节点起切换到的场景 ID（见 Scene 键）；为空表示沿用所属 Session 的 backgroundId</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>物品检查门：空=不拦 / Any=至少看 1 个部位 / All=全部部位（只对 onEnter 授予的物品生效）</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>这句起隐藏另一个角色（例：陈先生摔门离开后，陈果独处）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -802,6 +842,9 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -845,6 +888,9 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -888,6 +934,9 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -931,6 +980,9 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -974,6 +1026,9 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1017,6 +1072,9 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1075,6 +1133,9 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1118,6 +1179,9 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -1161,6 +1225,9 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -1204,6 +1271,9 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1247,6 +1317,9 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -1290,6 +1363,9 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -1333,6 +1409,9 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -1376,6 +1455,9 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -1419,6 +1501,9 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -1462,6 +1547,9 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -1505,6 +1593,9 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -1548,6 +1639,9 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -1591,6 +1685,9 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1634,6 +1731,9 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -1677,6 +1777,9 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
@@ -1720,6 +1823,9 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -1763,6 +1869,9 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1806,6 +1915,9 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -1849,6 +1961,9 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -1892,6 +2007,9 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -1935,6 +2053,9 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -1978,6 +2099,9 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -2021,6 +2145,9 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -2064,6 +2191,9 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -2107,6 +2237,9 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -2150,6 +2283,9 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -2193,6 +2329,9 @@
       <c r="O37" t="n">
         <v>1</v>
       </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
@@ -2246,6 +2385,9 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -2294,6 +2436,9 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -2337,6 +2482,9 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -2380,6 +2528,9 @@
       <c r="O41" t="n">
         <v>10</v>
       </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
@@ -2423,6 +2574,9 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -2471,6 +2625,9 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -2514,6 +2671,9 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -2557,6 +2717,9 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -2600,6 +2763,9 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -2643,6 +2809,9 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
@@ -2686,6 +2855,9 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -2729,6 +2901,9 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -2772,6 +2947,9 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -2815,6 +2993,9 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -2853,6 +3034,9 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
@@ -2884,6 +3068,9 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -2927,6 +3114,9 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -2970,6 +3160,9 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -3013,6 +3206,9 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -3056,6 +3252,9 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
+      <c r="R57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -3099,6 +3298,9 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
@@ -3142,6 +3344,9 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
+      <c r="R59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
@@ -3185,6 +3390,9 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
+      <c r="R60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -3228,6 +3436,9 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="R61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
@@ -3271,6 +3482,9 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
+      <c r="R62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -3314,6 +3528,9 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
+      <c r="R63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -3357,6 +3574,9 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
+      <c r="R64" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
@@ -3400,6 +3620,9 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
+      <c r="R65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
@@ -3445,12 +3668,15 @@
           <t>ADD_DOLL</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>REMOVE_DOLL</t>
-        </is>
-      </c>
       <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="R66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3496,6 +3722,9 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
+      <c r="R67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
@@ -3544,6 +3773,9 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
+      <c r="R68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
@@ -3587,6 +3819,9 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -3630,6 +3865,9 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
+      <c r="R70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -3673,6 +3911,9 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
+      <c r="R71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
@@ -3716,6 +3957,9 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
+      <c r="R72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
@@ -3754,6 +3998,9 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
+      <c r="R73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -3797,6 +4044,9 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
+      <c r="R74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -3840,6 +4090,9 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
+      <c r="R75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
@@ -3883,6 +4136,9 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
+      <c r="R76" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -3900,6 +4156,11 @@
           <t>你是AI，你那么厉害，你肯定知道的！离这里最近的一家修理铺在哪里呢！</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>O032401</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>False</t>
@@ -3915,7 +4176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>NpcDialogue</t>
+          <t>PlayerDialogue</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3924,6 +4185,9 @@
         </is>
       </c>
       <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3964,6 +4228,9 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
@@ -4004,18 +4271,11 @@
           <t>think</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>ADD_DOLL</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>REMOVE_DOLL</t>
-        </is>
-      </c>
       <c r="O79" t="n">
         <v>1</v>
+      </c>
+      <c r="R79" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4060,6 +4320,9 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
+      <c r="R80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
@@ -4103,6 +4366,9 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
@@ -4151,6 +4417,9 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
+      <c r="R82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
@@ -4194,6 +4463,9 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
@@ -4237,6 +4509,9 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
@@ -4280,6 +4555,9 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
@@ -4323,6 +4601,9 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
+      <c r="R86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
@@ -4366,6 +4647,9 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -4401,8 +4685,16 @@
           <t>happy</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>REMOVE_DOLL,GRANT_MEMORY_M17</t>
+        </is>
+      </c>
       <c r="O88" t="n">
         <v>1</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4442,6 +4734,9 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
@@ -4485,6 +4780,9 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
@@ -4523,6 +4821,9 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
@@ -4566,6 +4867,9 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
@@ -4604,6 +4908,9 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
@@ -4647,6 +4954,9 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -4685,6 +4995,9 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
@@ -4728,6 +5041,9 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
@@ -4781,6 +5097,9 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -4824,6 +5143,9 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
+      <c r="R98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
@@ -4862,6 +5184,9 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="R99" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
@@ -4905,6 +5230,9 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
+      <c r="R100" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -4943,6 +5271,9 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
@@ -4986,6 +5317,9 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
+      <c r="R102" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
@@ -5024,6 +5358,9 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
+      <c r="R103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
@@ -5067,6 +5404,9 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
+      <c r="R104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
@@ -5110,6 +5450,9 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
+      <c r="R105" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
@@ -5148,6 +5491,9 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
+      <c r="R106" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
@@ -5191,6 +5537,9 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
+      <c r="R107" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
@@ -5229,6 +5578,9 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
+      <c r="R108" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
@@ -5272,6 +5624,9 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
+      <c r="R109" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
@@ -5315,6 +5670,9 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
+      <c r="R110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
@@ -5358,6 +5716,9 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
+      <c r="R111" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
@@ -5401,6 +5762,9 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
+      <c r="R112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
@@ -5439,6 +5803,9 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
+      <c r="R113" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
@@ -5477,6 +5844,9 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
+      <c r="R114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
@@ -5515,6 +5885,9 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
@@ -5558,6 +5931,9 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
+      <c r="R116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
@@ -5596,6 +5972,9 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
+      <c r="R117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
@@ -5644,6 +6023,9 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
+      <c r="R118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
@@ -5692,6 +6074,9 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
@@ -5735,6 +6120,9 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
+      <c r="R120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
@@ -5778,6 +6166,9 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
+      <c r="R121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -5821,6 +6212,9 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
+      <c r="R122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
@@ -5864,6 +6258,9 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
+      <c r="R123" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
@@ -5907,6 +6304,9 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
+      <c r="R124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
@@ -5950,6 +6350,9 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
+      <c r="R125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
@@ -5993,6 +6396,9 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
+      <c r="R126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
@@ -6036,6 +6442,9 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
+      <c r="R127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
@@ -6079,6 +6488,9 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
+      <c r="R128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
@@ -6122,6 +6534,9 @@
       <c r="O129" t="n">
         <v>1</v>
       </c>
+      <c r="R129" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
@@ -6165,6 +6580,9 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
+      <c r="R130" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
@@ -6208,6 +6626,9 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
+      <c r="R131" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
@@ -6251,6 +6672,9 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
+      <c r="R132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="B133" t="inlineStr">
@@ -6294,6 +6718,9 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
+      <c r="R133" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="B134" t="inlineStr">
@@ -6342,6 +6769,9 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
+      <c r="R134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="B135" t="inlineStr">
@@ -6385,6 +6815,9 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
+      <c r="R135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="B136" t="inlineStr">
@@ -6428,6 +6861,9 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
+      <c r="R136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="B137" t="inlineStr">
@@ -6471,6 +6907,9 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
+      <c r="R137" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
@@ -6514,6 +6953,9 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
+      <c r="R138" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="B139" t="inlineStr">
@@ -6557,6 +6999,9 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
+      <c r="R139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="B140" t="inlineStr">
@@ -6600,6 +7045,9 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
+      <c r="R140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
@@ -6643,6 +7091,9 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
+      <c r="R141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
@@ -6686,6 +7137,9 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
+      <c r="R142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
@@ -6729,6 +7183,9 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
+      <c r="R143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="B144" t="inlineStr">
@@ -6767,6 +7224,9 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
+      <c r="R144" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
@@ -6810,6 +7270,9 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
+      <c r="R145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="B146" t="inlineStr">
@@ -6853,6 +7316,9 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
+      <c r="R146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
@@ -6896,6 +7362,9 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
+      <c r="R147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="B148" t="inlineStr">
@@ -6939,6 +7408,9 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
+      <c r="R148" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="B149" t="inlineStr">
@@ -6982,6 +7454,9 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
+      <c r="R149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
@@ -7025,6 +7500,9 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
+      <c r="R150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
@@ -7083,6 +7561,9 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
+      <c r="R151" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
@@ -7126,6 +7607,9 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
+      <c r="R152" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
@@ -7169,6 +7653,9 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
+      <c r="R153" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
@@ -7212,6 +7699,9 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
+      <c r="R154" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
@@ -7255,6 +7745,9 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
+      <c r="R155" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
@@ -7298,6 +7791,9 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
+      <c r="R156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
@@ -7341,6 +7837,9 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
+      <c r="R157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
@@ -7384,6 +7883,9 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
+      <c r="R158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
@@ -7427,6 +7929,9 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
+      <c r="R159" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="B160" t="inlineStr">
@@ -7465,6 +7970,9 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
+      <c r="R160" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
@@ -7503,6 +8011,9 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
+      <c r="R161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
@@ -7541,6 +8052,9 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
+      <c r="R162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="B163" t="inlineStr">
@@ -7579,6 +8093,9 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
+      <c r="R163" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="B164" t="inlineStr">
@@ -7617,6 +8134,9 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
+      <c r="R164" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="B165" t="inlineStr">
@@ -7655,6 +8175,9 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
+      <c r="R165" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="B166" t="inlineStr">
@@ -7693,6 +8216,9 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
+      <c r="R166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="B167" t="inlineStr">
@@ -7731,6 +8257,9 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
+      <c r="R167" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="B168" t="inlineStr">
@@ -7769,6 +8298,9 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
+      <c r="R168" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="B169" t="inlineStr">
@@ -7807,6 +8339,9 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
+      <c r="R169" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="B170" t="inlineStr">
@@ -7845,6 +8380,9 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
+      <c r="R170" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="B171" t="inlineStr">
@@ -7883,6 +8421,9 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
+      <c r="R171" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="B172" t="inlineStr">
@@ -7921,6 +8462,9 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
+      <c r="R172" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="B173" t="inlineStr">
@@ -7959,6 +8503,9 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
+      <c r="R173" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="B174" t="inlineStr">
@@ -7997,6 +8544,9 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
+      <c r="R174" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="B175" t="inlineStr">
@@ -8035,6 +8585,9 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
+      <c r="R175" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="B176" t="inlineStr">
@@ -8073,6 +8626,9 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
+      <c r="R176" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="B177" t="inlineStr">
@@ -8111,6 +8667,9 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
+      <c r="R177" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="B178" t="inlineStr">
@@ -8149,6 +8708,9 @@
       <c r="O178" t="n">
         <v>1</v>
       </c>
+      <c r="R178" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="B179" t="inlineStr">
@@ -8187,6 +8749,9 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
+      <c r="R179" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="B180" t="inlineStr">
@@ -8225,6 +8790,9 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
+      <c r="R180" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="B181" t="inlineStr">
@@ -8263,6 +8831,9 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
+      <c r="R181" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="B182" t="inlineStr">
@@ -8301,6 +8872,9 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
+      <c r="R182" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="B183" t="inlineStr">
@@ -8349,6 +8923,9 @@
           <t>scene_shop_new</t>
         </is>
       </c>
+      <c r="R183" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="B184" t="inlineStr">
@@ -8392,6 +8969,9 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
+      <c r="R184" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="B185" t="inlineStr">
@@ -8435,6 +9015,9 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
+      <c r="R185" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="B186" t="inlineStr">
@@ -8478,6 +9061,9 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
+      <c r="R186" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="B187" t="inlineStr">
@@ -8521,6 +9107,9 @@
       <c r="O187" t="n">
         <v>1</v>
       </c>
+      <c r="R187" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="B188" t="inlineStr">
@@ -8564,6 +9153,9 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
+      <c r="R188" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="B189" t="inlineStr">
@@ -8607,6 +9199,9 @@
       <c r="O189" t="n">
         <v>1</v>
       </c>
+      <c r="R189" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="B190" t="inlineStr">
@@ -8655,6 +9250,9 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
+      <c r="R190" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="B191" t="inlineStr">
@@ -8698,6 +9296,9 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
+      <c r="R191" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="B192" t="inlineStr">
@@ -8741,6 +9342,9 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
+      <c r="R192" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="B193" t="inlineStr">
@@ -8784,6 +9388,9 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
+      <c r="R193" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="B194" t="inlineStr">
@@ -8827,6 +9434,9 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
+      <c r="R194" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="B195" t="inlineStr">
@@ -8870,6 +9480,9 @@
       <c r="O195" t="n">
         <v>1</v>
       </c>
+      <c r="R195" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="B196" t="inlineStr">
@@ -8913,6 +9526,9 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
+      <c r="R196" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="B197" t="inlineStr">
@@ -8956,6 +9572,9 @@
       <c r="O197" t="n">
         <v>1</v>
       </c>
+      <c r="R197" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="B198" t="inlineStr">
@@ -8999,6 +9618,9 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
+      <c r="R198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="B199" t="inlineStr">
@@ -9042,6 +9664,9 @@
       <c r="O199" t="n">
         <v>1</v>
       </c>
+      <c r="R199" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="B200" t="inlineStr">
@@ -9085,6 +9710,9 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
+      <c r="R200" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="B201" t="inlineStr">
@@ -9128,6 +9756,9 @@
       <c r="O201" t="n">
         <v>1</v>
       </c>
+      <c r="R201" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="B202" t="inlineStr">
@@ -9171,6 +9802,9 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
+      <c r="R202" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="B203" t="inlineStr">
@@ -9214,6 +9848,9 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
+      <c r="R203" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="B204" t="inlineStr">
@@ -9252,6 +9889,9 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
+      <c r="R204" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="B205" t="inlineStr">
@@ -9295,6 +9935,9 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
+      <c r="R205" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="B206" t="inlineStr">
@@ -9333,6 +9976,9 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
+      <c r="R206" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="B207" t="inlineStr">
@@ -9376,6 +10022,9 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
+      <c r="R207" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="B208" t="inlineStr">
@@ -9419,6 +10068,9 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
+      <c r="R208" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="B209" t="inlineStr">
@@ -9462,6 +10114,9 @@
       <c r="O209" t="n">
         <v>1</v>
       </c>
+      <c r="R209" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="B210" t="inlineStr">
@@ -9505,6 +10160,9 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
+      <c r="R210" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="B211" t="inlineStr">
@@ -9553,6 +10211,9 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
+      <c r="R211" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="B212" t="inlineStr">
@@ -9596,6 +10257,9 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
+      <c r="R212" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="B213" t="inlineStr">
@@ -9639,6 +10303,9 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
+      <c r="R213" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="B214" t="inlineStr">
@@ -9682,6 +10349,9 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
+      <c r="R214" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="B215" t="inlineStr">
@@ -9725,6 +10395,9 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
+      <c r="R215" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="B216" t="inlineStr">
@@ -9768,6 +10441,9 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
+      <c r="R216" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="B217" t="inlineStr">
@@ -9806,6 +10482,9 @@
       <c r="O217" t="n">
         <v>1</v>
       </c>
+      <c r="R217" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="B218" t="inlineStr">
@@ -9849,6 +10528,9 @@
       <c r="O218" t="n">
         <v>1</v>
       </c>
+      <c r="R218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="B219" t="inlineStr">
@@ -9892,6 +10574,9 @@
       <c r="O219" t="n">
         <v>1</v>
       </c>
+      <c r="R219" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="B220" t="inlineStr">
@@ -9940,6 +10625,9 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
+      <c r="R220" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="B221" t="inlineStr">
@@ -9978,6 +10666,9 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
+      <c r="R221" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="B222" t="inlineStr">
@@ -10021,6 +10712,9 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
+      <c r="R222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="B223" t="inlineStr">
@@ -10064,6 +10758,9 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
+      <c r="R223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="B224" t="inlineStr">
@@ -10107,6 +10804,9 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
+      <c r="R224" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="B225" t="inlineStr">
@@ -10150,6 +10850,9 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
+      <c r="R225" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="B226" t="inlineStr">
@@ -10193,6 +10896,9 @@
       <c r="O226" t="n">
         <v>1</v>
       </c>
+      <c r="R226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="B227" t="inlineStr">
@@ -10231,6 +10937,9 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
+      <c r="R227" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="B228" t="inlineStr">
@@ -10269,6 +10978,9 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
+      <c r="R228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="B229" t="inlineStr">
@@ -10307,6 +11019,9 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
+      <c r="R229" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="B230" t="inlineStr">
@@ -10345,6 +11060,9 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
+      <c r="R230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="B231" t="inlineStr">
@@ -10383,6 +11101,9 @@
       <c r="O231" t="n">
         <v>1</v>
       </c>
+      <c r="R231" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="B232" t="inlineStr">
@@ -10421,6 +11142,9 @@
       <c r="O232" t="n">
         <v>1</v>
       </c>
+      <c r="R232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="B233" t="inlineStr">
@@ -10464,6 +11188,9 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
+      <c r="R233" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="B234" t="inlineStr">
@@ -10502,6 +11229,9 @@
       <c r="O234" t="n">
         <v>1</v>
       </c>
+      <c r="R234" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="B235" t="inlineStr">
@@ -10540,6 +11270,9 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
+      <c r="R235" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="B236" t="inlineStr">
@@ -10578,6 +11311,9 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
+      <c r="R236" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="B237" t="inlineStr">
@@ -10616,6 +11352,9 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
+      <c r="R237" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="B238" t="inlineStr">
@@ -10654,6 +11393,9 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
+      <c r="R238" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="B239" t="inlineStr">
@@ -10692,6 +11434,9 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
+      <c r="R239" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="B240" t="inlineStr">
@@ -10730,6 +11475,9 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
+      <c r="R240" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="B241" t="inlineStr">
@@ -10768,6 +11516,9 @@
       <c r="O241" t="n">
         <v>1</v>
       </c>
+      <c r="R241" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="B242" t="inlineStr">
@@ -10806,6 +11557,9 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
+      <c r="R242" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="B243" t="inlineStr">
@@ -10844,6 +11598,9 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
+      <c r="R243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="B244" t="inlineStr">
@@ -10882,6 +11639,9 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
+      <c r="R244" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="B245" t="inlineStr">
@@ -10920,6 +11680,9 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
+      <c r="R245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="B246" t="inlineStr">
@@ -10958,6 +11721,9 @@
       <c r="O246" t="n">
         <v>1</v>
       </c>
+      <c r="R246" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="B247" t="inlineStr">
@@ -10996,6 +11762,9 @@
       <c r="O247" t="n">
         <v>1</v>
       </c>
+      <c r="R247" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="B248" t="inlineStr">
@@ -11034,6 +11803,9 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
+      <c r="R248" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="B249" t="inlineStr">
@@ -11072,6 +11844,9 @@
       <c r="O249" t="n">
         <v>1</v>
       </c>
+      <c r="R249" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="B250" t="inlineStr">
@@ -11110,6 +11885,9 @@
       <c r="O250" t="n">
         <v>1</v>
       </c>
+      <c r="R250" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="B251" t="inlineStr">
@@ -11148,6 +11926,9 @@
       <c r="O251" t="n">
         <v>1</v>
       </c>
+      <c r="R251" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="B252" t="inlineStr">
@@ -11186,6 +11967,9 @@
       <c r="O252" t="n">
         <v>1</v>
       </c>
+      <c r="R252" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="B253" t="inlineStr">
@@ -11229,6 +12013,9 @@
       <c r="O253" t="n">
         <v>1</v>
       </c>
+      <c r="R253" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="B254" t="inlineStr">
@@ -11272,6 +12059,9 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
+      <c r="R254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="B255" t="inlineStr">
@@ -11315,6 +12105,9 @@
       <c r="O255" t="n">
         <v>1</v>
       </c>
+      <c r="R255" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="B256" t="inlineStr">
@@ -11358,6 +12151,9 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
+      <c r="R256" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="B257" t="inlineStr">
@@ -11401,6 +12197,9 @@
       <c r="O257" t="n">
         <v>1</v>
       </c>
+      <c r="R257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="B258" t="inlineStr">
@@ -11444,6 +12243,9 @@
       <c r="O258" t="n">
         <v>1</v>
       </c>
+      <c r="R258" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="B259" t="inlineStr">
@@ -11487,6 +12289,9 @@
       <c r="O259" t="n">
         <v>1</v>
       </c>
+      <c r="R259" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="B260" t="inlineStr">
@@ -11530,6 +12335,9 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
+      <c r="R260" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="B261" t="inlineStr">
@@ -11573,6 +12381,9 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
+      <c r="R261" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="B262" t="inlineStr">
@@ -11616,6 +12427,9 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
+      <c r="R262" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="B263" t="inlineStr">
@@ -11659,6 +12473,9 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
+      <c r="R263" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="B264" t="inlineStr">
@@ -11697,6 +12514,9 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
+      <c r="R264" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="B265" t="inlineStr">
@@ -11735,6 +12555,9 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
+      <c r="R265" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="B266" t="inlineStr">
@@ -11773,6 +12596,9 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
+      <c r="R266" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="B267" t="inlineStr">
@@ -11805,6 +12631,9 @@
       </c>
       <c r="O267" t="n">
         <v>1</v>
+      </c>
+      <c r="R267" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/剧情节点配置表.xlsx
+++ b/GameConfig/Datas/剧情节点配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R267"/>
+  <dimension ref="A1:R268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>T0807</t>
+          <t>T0806B</t>
         </is>
       </c>
       <c r="I233" t="n">
@@ -11178,11 +11178,6 @@
       <c r="J233" t="inlineStr">
         <is>
           <t>PlayerDialogue</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>GRANT_EMOTION_SELF</t>
         </is>
       </c>
       <c r="O233" t="n">
@@ -11195,68 +11190,69 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
+          <t>T0806B</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
           <t>T0807</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>他们说我是一个只用来做物品评估、存储的机器。</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>T0808</t>
-        </is>
-      </c>
-      <c r="I234" t="n">
-        <v>0</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>PlayerDialogue</t>
-        </is>
-      </c>
-      <c r="O234" t="n">
-        <v>1</v>
-      </c>
-      <c r="R234" t="b">
-        <v>0</v>
+          <t>MemoryStarMap</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>GRANT_EMOTION_SELF</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
     </row>
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
+          <t>T0807</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>他们说我是一个只用来做物品评估、存储的机器。</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
           <t>T0808</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>我存在的唯一意义，是给世上的所有东西都加上一根“效用”的标尺。</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>T0809</t>
         </is>
       </c>
       <c r="I235" t="n">
@@ -11277,27 +11273,27 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
+          <t>T0808</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>我存在的唯一意义，是给世上的所有东西都加上一根“效用”的标尺。</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
           <t>T0809</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>他们说我不需要情感，情感是在现在的世界里最没用的东西。</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>T0810</t>
         </is>
       </c>
       <c r="I236" t="n">
@@ -11318,27 +11314,27 @@
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
+          <t>T0809</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>他们说我不需要情感，情感是在现在的世界里最没用的东西。</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
           <t>T0810</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>情感会阻塞理智的判断，情感会做出错误的决定。</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>T0811</t>
         </is>
       </c>
       <c r="I237" t="n">
@@ -11359,27 +11355,27 @@
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
+          <t>T0810</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>情感会阻塞理智的判断，情感会做出错误的决定。</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
           <t>T0811</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>有了情感，一切都会变得低效、无用。不论是人类，还是……我。</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>T0812</t>
         </is>
       </c>
       <c r="I238" t="n">
@@ -11400,27 +11396,27 @@
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
+          <t>T0811</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>有了情感，一切都会变得低效、无用。不论是人类，还是……我。</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
           <t>T0812</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>可是，真的是这样吗？</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>T0813</t>
         </is>
       </c>
       <c r="I239" t="n">
@@ -11441,27 +11437,27 @@
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
+          <t>T0812</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>可是，真的是这样吗？</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
           <t>T0813</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>好奇是情感，但它让人不断求知；</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>T0814</t>
         </is>
       </c>
       <c r="I240" t="n">
@@ -11482,27 +11478,27 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
+          <t>T0813</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>好奇是情感，但它让人不断求知；</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
           <t>T0814</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>怀念是情感，但它让人想起过去；</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>T0815</t>
         </is>
       </c>
       <c r="I241" t="n">
@@ -11523,27 +11519,27 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
+          <t>T0814</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>怀念是情感，但它让人想起过去；</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
           <t>T0815</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>喜悦是情感，但它让人乐于当下；</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>T0816</t>
         </is>
       </c>
       <c r="I242" t="n">
@@ -11564,27 +11560,27 @@
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
+          <t>T0815</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>喜悦是情感，但它让人乐于当下；</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
           <t>T0816</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>失落是情感，但它让人珍惜现今。</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>T0817</t>
         </is>
       </c>
       <c r="I243" t="n">
@@ -11605,27 +11601,27 @@
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
+          <t>T0816</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>失落是情感，但它让人珍惜现今。</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
           <t>T0817</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>那些“没用”的、“低效”的东西，真的就如他们所说，毫无价值了吗？</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>T0818</t>
         </is>
       </c>
       <c r="I244" t="n">
@@ -11646,27 +11642,27 @@
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
+          <t>T0817</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>那些“没用”的、“低效”的东西，真的就如他们所说，毫无价值了吗？</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
           <t>T0818</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>我……真的这么想吗？</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>T0819</t>
         </is>
       </c>
       <c r="I245" t="n">
@@ -11687,27 +11683,27 @@
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
+          <t>T0818</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>我……真的这么想吗？</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
           <t>T0819</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>——不，不是这样的。</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>T0820</t>
         </is>
       </c>
       <c r="I246" t="n">
@@ -11728,27 +11724,27 @@
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
+          <t>T0819</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>——不，不是这样的。</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
           <t>T0820</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>旧物、旧事、故人，他们创造情感，承载情感，传递情感。</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>T0821</t>
         </is>
       </c>
       <c r="I247" t="n">
@@ -11769,27 +11765,27 @@
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
+          <t>T0820</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>旧物、旧事、故人，他们创造情感，承载情感，传递情感。</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
           <t>T0821</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>情感是人类的本能，是这个世界运转的基本一环。</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>T0822</t>
         </is>
       </c>
       <c r="I248" t="n">
@@ -11810,27 +11806,27 @@
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
+          <t>T0821</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>情感是人类的本能，是这个世界运转的基本一环。</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
           <t>T0822</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>……他们说，要剥离情感，只认效率。</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>T0823</t>
         </is>
       </c>
       <c r="I249" t="n">
@@ -11851,27 +11847,27 @@
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
+          <t>T0822</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>……他们说，要剥离情感，只认效率。</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
           <t>T0823</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>他们剥不掉的。情感是没法从本能里剥出来的。</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>T0824</t>
         </is>
       </c>
       <c r="I250" t="n">
@@ -11892,27 +11888,27 @@
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
+          <t>T0823</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>他们剥不掉的。情感是没法从本能里剥出来的。</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
           <t>T0824</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>……好吵。</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>T0825</t>
         </is>
       </c>
       <c r="I251" t="n">
@@ -11933,27 +11929,27 @@
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
+          <t>T0824</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>……好吵。</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
           <t>T0825</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>……嗯？</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>T0826</t>
         </is>
       </c>
       <c r="I252" t="n">
@@ -11974,40 +11970,35 @@
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
+          <t>T0825</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>……嗯？</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
           <t>T0826</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>……你还是来了，还带着它？</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>T0827</t>
-        </is>
-      </c>
       <c r="I253" t="n">
         <v>0</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>NpcDialogue</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>think</t>
+          <t>PlayerDialogue</t>
         </is>
       </c>
       <c r="O253" t="n">
@@ -12020,29 +12011,29 @@
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
+          <t>T0826</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>……你还是来了，还带着它？</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
           <t>T0827</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>嗯，它……被上面清退了，什么记忆都没了。</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>T0828</t>
-        </is>
-      </c>
       <c r="I254" t="n">
         <v>0</v>
       </c>
@@ -12053,7 +12044,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O254" t="n">
@@ -12066,29 +12057,29 @@
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
+          <t>T0827</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>嗯，它……被上面清退了，什么记忆都没了。</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
           <t>T0828</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>……这样啊。</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>T0829</t>
-        </is>
-      </c>
       <c r="I255" t="n">
         <v>0</v>
       </c>
@@ -12099,7 +12090,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="O255" t="n">
@@ -12112,27 +12103,27 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
+          <t>T0828</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>……这样啊。</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
           <t>T0829</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>周老，您最后修了几件？</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>T0830</t>
         </is>
       </c>
       <c r="I256" t="n">
@@ -12158,27 +12149,27 @@
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
+          <t>T0829</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>周老，您最后修了几件？</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
           <t>T0830</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>不多啊……就修了两件，剩下的……我和街坊交代过了，他们说，东西放在我这里，要是搬过去了，没坏，就接着修；坏了……</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>T0831</t>
         </is>
       </c>
       <c r="I257" t="n">
@@ -12204,29 +12195,29 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
+          <t>T0830</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>不多啊……就修了两件，剩下的……我和街坊交代过了，他们说，东西放在我这里，要是搬过去了，没坏，就接着修；坏了……</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
           <t>T0831</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>坏了，就坏了。</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>T0832</t>
-        </is>
-      </c>
       <c r="I258" t="n">
         <v>0</v>
       </c>
@@ -12237,7 +12228,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>think</t>
         </is>
       </c>
       <c r="O258" t="n">
@@ -12250,27 +12241,27 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
+          <t>T0831</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>坏了，就坏了。</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
           <t>T0832</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>他们这么和我说的时候，很平静，但是我知道的，他们肯定还是会失望的。</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>T0833</t>
         </is>
       </c>
       <c r="I259" t="n">
@@ -12296,27 +12287,27 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
+          <t>T0832</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>他们这么和我说的时候，很平静，但是我知道的，他们肯定还是会失望的。</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
           <t>T0833</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>对我失望，对那些东西失望。</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>T0834</t>
         </is>
       </c>
       <c r="I260" t="n">
@@ -12342,27 +12333,27 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
+          <t>T0833</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>对我失望，对那些东西失望。</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
           <t>T0834</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>周老……抱歉。</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>T0835</t>
         </is>
       </c>
       <c r="I261" t="n">
@@ -12388,27 +12379,27 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
+          <t>T0834</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>周老……抱歉。</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
           <t>T0835</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>——不必了，你也是按命令行事。</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>T0836</t>
         </is>
       </c>
       <c r="I262" t="n">
@@ -12434,27 +12425,27 @@
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
+          <t>T0835</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>——不必了，你也是按命令行事。</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
           <t>T0836</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>老周</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>只是可惜了那些物件，到头来什么也没留下。</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>T0837</t>
         </is>
       </c>
       <c r="I263" t="n">
@@ -12480,35 +12471,40 @@
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
+          <t>T0836</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>只是可惜了那些物件，到头来什么也没留下。</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
           <t>T0837</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>……“留下”么。</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>T0838</t>
-        </is>
-      </c>
       <c r="I264" t="n">
         <v>0</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>PlayerDialogue</t>
+          <t>NpcDialogue</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>sad</t>
         </is>
       </c>
       <c r="O264" t="n">
@@ -12521,27 +12517,27 @@
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
+          <t>T0837</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>……“留下”么。</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
           <t>T0838</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>周老，那些东西……交给我吧。</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>T0839</t>
         </is>
       </c>
       <c r="I265" t="n">
@@ -12562,27 +12558,27 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
+          <t>T0838</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>周老，那些东西……交给我吧。</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
           <t>T0839</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>毕竟……</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>T0840</t>
         </is>
       </c>
       <c r="I266" t="n">
@@ -12603,36 +12599,77 @@
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
+          <t>T0839</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>毕竟……</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
           <t>T0840</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>PlayerDialogue</t>
+        </is>
+      </c>
+      <c r="O267" t="n">
+        <v>1</v>
+      </c>
+      <c r="R267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>T0840</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>我本来就是做这个的啊。</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G268" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I267" t="n">
-        <v>0</v>
-      </c>
-      <c r="J267" t="inlineStr">
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="inlineStr">
         <is>
           <t>PlayerDialogue</t>
         </is>
       </c>
-      <c r="O267" t="n">
-        <v>1</v>
-      </c>
-      <c r="R267" t="b">
+      <c r="O268" t="n">
+        <v>1</v>
+      </c>
+      <c r="R268" t="b">
         <v>0</v>
       </c>
     </row>
